--- a/data/trending_integrated_20261023_13.xlsx
+++ b/data/trending_integrated_20261023_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2035</v>
+        <v>1985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+24.46%</t>
+          <t>'+21.41%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.14</v>
       </c>
       <c r="E2" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="F2" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G2" t="n">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="H2" t="n">
         <v>4.87</v>
@@ -610,7 +610,7 @@
         <v>5.01</v>
       </c>
       <c r="O2" t="n">
-        <v>57092649716</v>
+        <v>60173736150</v>
       </c>
       <c r="P2" t="n">
         <v>4980</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세 및 휴머노이드, AI 기술 기반 급등 기대, 외인 매수세 유입.</t>
+          <t>로봇 관련 사업 상용화 기대감과 함께 대형주(삼성)와의 연계 가능성, 외인 매수세 유입 등을 언급하며 상승을 전망하는 게시글.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇', '휴머노이드', '외인']</t>
+          <t>['로봇 사업', '휴머노이드', '외인 매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60700</v>
+        <v>60900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.57%</t>
+          <t>'+9.93%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F3" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G3" t="n">
-        <v>998</v>
+        <v>1015</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>569644868400</v>
+        <v>577913410150</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -711,10 +711,10 @@
         <v>23150</v>
       </c>
       <c r="R3" t="n">
-        <v>1319000</v>
+        <v>1515000</v>
       </c>
       <c r="S3" t="n">
-        <v>8000</v>
+        <v>42000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4005</v>
+        <v>4040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.80%</t>
+          <t>'+7.73%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="F4" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G4" t="n">
-        <v>734</v>
+        <v>840</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>143549085402</v>
+        <v>145165679099</v>
       </c>
       <c r="P4" t="n">
         <v>7050</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 이슈 속 외인 매도 및 주가 조작 논란, 전쟁 관련 기대감.</t>
+          <t>북한 관련 지정학적 리스크 부각과 함께 방산주로서의 상승 가능성을 언급하는 게시글.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['북한', '코브라볼', '공매도']</t>
+          <t>['북한 리스크', '방산주', '김정은']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="G5" t="n">
-        <v>1348</v>
+        <v>1301</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -877,7 +877,7 @@
         <v>1200000</v>
       </c>
       <c r="L5" t="n">
-        <v>1257000</v>
+        <v>1263000</v>
       </c>
       <c r="M5" t="n">
         <v>1171000</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>2746730430500</v>
+        <v>2862666595500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -895,23 +895,23 @@
         <v>468000</v>
       </c>
       <c r="R5" t="n">
-        <v>-339000</v>
+        <v>-401000</v>
       </c>
       <c r="S5" t="n">
-        <v>94000</v>
+        <v>166000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 이슈 속에서 상승 시작 가능성 언급, 단기 고점 경고 및 적정 주가 제시.</t>
+          <t>국민연금 및 호남 반도체 관련 정치적 언급과 함께 일부 상승 및 하락에 대한 기대감이 혼재된 게시글.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['IPO', '반도체', '공매도']</t>
+          <t>['국민연금', '호남 반도체', '주가 전망']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H6" t="n">
         <v>2.92</v>
@@ -978,7 +978,7 @@
         <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>56940821245</v>
+        <v>57769769695</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>유리기판 사업 관련 삼성 인수설 및 EUV 기술 기반 상승 기대, 광섬유 품귀 현상.</t>
+          <t>EUV 유리기판 관련 기술력 및 삼성 인수설을 근거로 긍정적인 전망과 함께 외인 매수세 유입을 언급하는 게시글.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유리기판', 'EUV', '삼성']</t>
+          <t>['EUV 유리기판', '삼성 인수설', '광 섬유']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G7" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H7" t="n">
         <v>5.11</v>
@@ -1070,7 +1070,7 @@
         <v>5.15</v>
       </c>
       <c r="O7" t="n">
-        <v>6438341790</v>
+        <v>6473922450</v>
       </c>
       <c r="P7" t="n">
         <v>15900</v>
@@ -1079,14 +1079,14 @@
         <v>6310</v>
       </c>
       <c r="R7" t="n">
-        <v>-311000</v>
+        <v>-334000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>신약 개발 관련 기대와 우려 혼재, 약효 증명 부족 및 주가 하락 논란.</t>
+          <t>신약 개발 및 임상 관련 불확실성과 함께 주가 조작 및 단타 세력에 대한 부정적인 인식을 드러내는 게시글.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['신약', '3상', '주포']</t>
+          <t>['신약 개발', '주가 조작', '단타 세력']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14450</v>
+        <v>14520</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.55%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="H8" t="n">
         <v>9.890000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>25332877185</v>
+        <v>25618109715</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1171,14 +1171,14 @@
         <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>-96000</v>
+        <v>-63000</v>
       </c>
       <c r="S8" t="n">
-        <v>57000</v>
+        <v>69000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>이재명 대통령의 주가 조작 방관 비판. 3분기 실적 및 대차 해지 독려. 거래량 부족으로 인한 하락세 진정 및 주말 호재 기대.</t>
+          <t>3분기 실적 언급과 함께 주가 조작 및 이재명 대통령에 대한 강한 비판이 주를 이루는 게시글.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가 조작', '3분기 실적', '대차 해지']</t>
+          <t>['주가 조작', '실적 발표', '대통령 비판']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17250</v>
+        <v>213500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.58%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.48</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>86</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>54</v>
+        <v>501</v>
       </c>
       <c r="G9" t="n">
-        <v>143</v>
+        <v>1628</v>
       </c>
       <c r="H9" t="n">
-        <v>3.77</v>
+        <v>46.13</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17350</v>
+        <v>214500</v>
       </c>
       <c r="K9" t="n">
-        <v>18130</v>
+        <v>206000</v>
       </c>
       <c r="L9" t="n">
-        <v>19070</v>
+        <v>214500</v>
       </c>
       <c r="M9" t="n">
-        <v>16530</v>
+        <v>203500</v>
       </c>
       <c r="N9" t="n">
-        <v>3.29</v>
+        <v>46.14</v>
       </c>
       <c r="O9" t="n">
-        <v>48155847440</v>
+        <v>2177103723500</v>
       </c>
       <c r="P9" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>6320</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>-11000</v>
+        <v>-839000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>보안주 상승 및 AI 관련 긍정적 뉴스 언급. 주가 조작 및 최악의 무빙에 대한 불만도 제기.</t>
+          <t>이재명 정부의 정책에 대한 부정적 언급과 함께 시장 붕괴 가능성, 일부 반도체 주 상승 기대감이 혼재된 게시글.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '주가 조작']</t>
+          <t>['시장 붕괴', '정책 비판', '반도체 주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>213000</v>
+        <v>17100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.70%</t>
+          <t>'-1.44%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>0.48</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>87</v>
       </c>
       <c r="F10" t="n">
-        <v>497</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
-        <v>1571</v>
+        <v>145</v>
       </c>
       <c r="H10" t="n">
-        <v>46.13</v>
+        <v>3.77</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>214500</v>
+        <v>17350</v>
       </c>
       <c r="K10" t="n">
-        <v>206000</v>
+        <v>18130</v>
       </c>
       <c r="L10" t="n">
-        <v>213500</v>
+        <v>19070</v>
       </c>
       <c r="M10" t="n">
-        <v>203500</v>
+        <v>16530</v>
       </c>
       <c r="N10" t="n">
-        <v>46.14</v>
+        <v>3.29</v>
       </c>
       <c r="O10" t="n">
-        <v>2071626759000</v>
+        <v>48404906135</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>6320</v>
       </c>
       <c r="R10" t="n">
-        <v>-358000</v>
+        <v>-11000</v>
       </c>
       <c r="S10" t="n">
-        <v>82000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관된 부정적 전망 속 일부 긍정적 매수 의견 혼재.</t>
+          <t>보안주 상승 및 AI 관련 긍정적 뉴스 언급. 주가 조작 및 최악의 무빙에 대한 불만도 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['ETF', '연기금', '매수']</t>
+          <t>['보안주', 'AI', '주가 조작']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7100</v>
+        <v>7110</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.80%</t>
+          <t>'-1.66%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>132</v>
       </c>
       <c r="F11" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="H11" t="n">
         <v>25.42</v>
@@ -1438,7 +1438,7 @@
         <v>25.47</v>
       </c>
       <c r="O11" t="n">
-        <v>10871559835</v>
+        <v>11180938090</v>
       </c>
       <c r="P11" t="n">
         <v>17950</v>
@@ -1447,23 +1447,23 @@
         <v>7010</v>
       </c>
       <c r="R11" t="n">
-        <v>-54000</v>
+        <v>26000</v>
       </c>
       <c r="S11" t="n">
-        <v>13000</v>
+        <v>9000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>호실적 발표 및 외인/기관 순매수 기반 상승 기대, 목표가 제시.</t>
+          <t>3분기 순이익 7,556억 흑자 전환 및 재무 상태 개선을 근거로 주가 반등을 기대하는 게시글.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['순이익', 'BPS', '목표가']</t>
+          <t>['순이익 흑자', '재무 개선', '주가 반등']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16580</v>
+        <v>59000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.27%</t>
+          <t>'-4.22%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>101</v>
+        <v>254</v>
       </c>
       <c r="F12" t="n">
-        <v>66</v>
+        <v>159</v>
       </c>
       <c r="G12" t="n">
-        <v>220</v>
+        <v>649</v>
       </c>
       <c r="H12" t="n">
-        <v>27.89</v>
+        <v>22.25</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17320</v>
+        <v>61600</v>
       </c>
       <c r="K12" t="n">
-        <v>16810</v>
+        <v>59600</v>
       </c>
       <c r="L12" t="n">
-        <v>16850</v>
+        <v>60000</v>
       </c>
       <c r="M12" t="n">
-        <v>16450</v>
+        <v>57700</v>
       </c>
       <c r="N12" t="n">
-        <v>27.87</v>
+        <v>22.26</v>
       </c>
       <c r="O12" t="n">
-        <v>25050294065</v>
+        <v>97335885550</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>16450</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>16000</v>
+        <v>-203000</v>
       </c>
       <c r="S12" t="n">
-        <v>19000</v>
+        <v>-124000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관된 부정적 전망 속 조선주 약세 및 주주환원 정책 기대.</t>
+          <t>정치적 이슈와 증시 폭락 가능성 언급 속 공매도 우려 및 주가 하락 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['조선주', '주주환원', '신저점']</t>
+          <t>['공매도', '지수', '폭락']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>58700</v>
+        <v>16580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.71%</t>
+          <t>'-4.27%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>246</v>
+        <v>103</v>
       </c>
       <c r="F13" t="n">
-        <v>156</v>
+        <v>67</v>
       </c>
       <c r="G13" t="n">
-        <v>635</v>
+        <v>219</v>
       </c>
       <c r="H13" t="n">
-        <v>22.25</v>
+        <v>27.89</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>61600</v>
+        <v>17320</v>
       </c>
       <c r="K13" t="n">
-        <v>59600</v>
+        <v>16810</v>
       </c>
       <c r="L13" t="n">
-        <v>60000</v>
+        <v>16850</v>
       </c>
       <c r="M13" t="n">
-        <v>57700</v>
+        <v>16450</v>
       </c>
       <c r="N13" t="n">
-        <v>22.26</v>
+        <v>27.87</v>
       </c>
       <c r="O13" t="n">
-        <v>94071051150</v>
+        <v>26281442770</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>16450</v>
       </c>
       <c r="R13" t="n">
-        <v>-64000</v>
+        <v>111000</v>
       </c>
       <c r="S13" t="n">
-        <v>-100000</v>
+        <v>30000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈와 증시 폭락 가능성 언급 속 공매도 우려 및 주가 하락 전망.</t>
+          <t>조선주 전반의 하락세와 함께 민주당 정권 및 정치적 이슈에 대한 부정적인 언급이 다수 포함된 게시글.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '지수', '폭락']</t>
+          <t>['조선주 하락', '정치적 이슈', '주주 환원']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9290</v>
+        <v>9310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-7.93%</t>
+          <t>'-7.73%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>69</v>
       </c>
       <c r="G14" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="H14" t="n">
         <v>2.5</v>
@@ -1714,7 +1714,7 @@
         <v>3.69</v>
       </c>
       <c r="O14" t="n">
-        <v>44489949830</v>
+        <v>45449588605</v>
       </c>
       <c r="P14" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261023_13.xlsx
+++ b/data/trending_integrated_20261023_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1985</v>
+        <v>1933</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.41%</t>
+          <t>'+18.23%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.14</v>
       </c>
       <c r="E2" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F2" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="H2" t="n">
         <v>4.87</v>
@@ -610,7 +610,7 @@
         <v>5.01</v>
       </c>
       <c r="O2" t="n">
-        <v>60173736150</v>
+        <v>63502250851</v>
       </c>
       <c r="P2" t="n">
         <v>4980</v>
@@ -619,23 +619,23 @@
         <v>735</v>
       </c>
       <c r="R2" t="n">
-        <v>85000</v>
+        <v>-2000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇 관련 사업 상용화 기대감과 함께 대형주(삼성)와의 연계 가능성, 외인 매수세 유입 등을 언급하며 상승을 전망하는 게시글.</t>
+          <t>휴머노이드 배터리 충전 상용화 및 빅웨이브 로봇 CES 참여 기대감. 외인 매수세 유입.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇 사업', '휴머노이드', '외인 매수']</t>
+          <t>['휴머노이드', '빅웨이브', '외인매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60900</v>
+        <v>61100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.93%</t>
+          <t>'+10.29%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="F3" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="G3" t="n">
-        <v>1015</v>
+        <v>1037</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -693,7 +693,7 @@
         <v>56300</v>
       </c>
       <c r="L3" t="n">
-        <v>61000</v>
+        <v>61300</v>
       </c>
       <c r="M3" t="n">
         <v>56200</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>577913410150</v>
+        <v>609364133950</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -711,7 +711,7 @@
         <v>23150</v>
       </c>
       <c r="R3" t="n">
-        <v>1515000</v>
+        <v>1522000</v>
       </c>
       <c r="S3" t="n">
         <v>42000</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4040</v>
+        <v>4055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.73%</t>
+          <t>'+8.13%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F4" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G4" t="n">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>145165679099</v>
+        <v>146638727190</v>
       </c>
       <c r="P4" t="n">
         <v>7050</v>
@@ -803,7 +803,7 @@
         <v>2500</v>
       </c>
       <c r="R4" t="n">
-        <v>-250000</v>
+        <v>-251000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1257000</v>
+        <v>1248000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.78%</t>
+          <t>'+2.04%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="G5" t="n">
-        <v>1301</v>
+        <v>1327</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>2862666595500</v>
+        <v>2951084235000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -895,14 +895,14 @@
         <v>468000</v>
       </c>
       <c r="R5" t="n">
-        <v>-401000</v>
+        <v>-405000</v>
       </c>
       <c r="S5" t="n">
         <v>166000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>국민연금 및 호남 반도체 관련 정치적 언급과 함께 일부 상승 및 하락에 대한 기대감이 혼재된 게시글.</t>
+          <t>국민연금 관련 논란 및 호남 반도체 중단 언급. 주가 반등 및 상승 추세 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['국민연금', '호남 반도체', '주가 전망']</t>
+          <t>['국민연금', '호남반도체', '주가반등']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13430</v>
+        <v>8710</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+0.35%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>422</v>
+        <v>199</v>
       </c>
       <c r="H6" t="n">
-        <v>2.92</v>
+        <v>5.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13340</v>
+        <v>8680</v>
       </c>
       <c r="K6" t="n">
-        <v>12840</v>
+        <v>9410</v>
       </c>
       <c r="L6" t="n">
-        <v>13700</v>
+        <v>9460</v>
       </c>
       <c r="M6" t="n">
-        <v>12530</v>
+        <v>8640</v>
       </c>
       <c r="N6" t="n">
-        <v>3.48</v>
+        <v>5.15</v>
       </c>
       <c r="O6" t="n">
-        <v>57769769695</v>
+        <v>6526148710</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>15900</v>
       </c>
       <c r="Q6" t="n">
-        <v>1640</v>
+        <v>6310</v>
       </c>
       <c r="R6" t="n">
-        <v>-159000</v>
+        <v>-334000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>EUV 유리기판 관련 기술력 및 삼성 인수설을 근거로 긍정적인 전망과 함께 외인 매수세 유입을 언급하는 게시글.</t>
+          <t>뇌졸중 치료제 관련 특허 보유 및 3상 성공 가능성 언급. 신약 개발 외자 유치 및 합병 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['EUV 유리기판', '삼성 인수설', '광 섬유']</t>
+          <t>['뇌졸중치료제', '특허', '신약개발']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8700</v>
+        <v>13330</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.04</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F7" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G7" t="n">
-        <v>190</v>
+        <v>434</v>
       </c>
       <c r="H7" t="n">
-        <v>5.11</v>
+        <v>2.92</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8680</v>
+        <v>13340</v>
       </c>
       <c r="K7" t="n">
-        <v>9410</v>
+        <v>12840</v>
       </c>
       <c r="L7" t="n">
-        <v>9460</v>
+        <v>13700</v>
       </c>
       <c r="M7" t="n">
-        <v>8640</v>
+        <v>12530</v>
       </c>
       <c r="N7" t="n">
-        <v>5.15</v>
+        <v>3.48</v>
       </c>
       <c r="O7" t="n">
-        <v>6473922450</v>
+        <v>58767527235</v>
       </c>
       <c r="P7" t="n">
-        <v>15900</v>
+        <v>31500</v>
       </c>
       <c r="Q7" t="n">
-        <v>6310</v>
+        <v>1640</v>
       </c>
       <c r="R7" t="n">
-        <v>-334000</v>
+        <v>-190000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>신약 개발 및 임상 관련 불확실성과 함께 주가 조작 및 단타 세력에 대한 부정적인 인식을 드러내는 게시글.</t>
+          <t>EUV 유리기판 관련 기술성 및 삼성 인수설 언급. 광섬유 품귀 현상과 외인 매수세 확인.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['신약 개발', '주가 조작', '단타 세력']</t>
+          <t>['유리기판', '삼성인수', '광섬유']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14520</v>
+        <v>14470</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.07%</t>
+          <t>'-0.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="H8" t="n">
         <v>9.890000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>25618109715</v>
+        <v>25977928745</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1171,7 +1171,7 @@
         <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>-63000</v>
+        <v>-62000</v>
       </c>
       <c r="S8" t="n">
         <v>69000</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>213500</v>
+        <v>212500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.47%</t>
+          <t>'-0.93%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="G9" t="n">
-        <v>1628</v>
+        <v>1600</v>
       </c>
       <c r="H9" t="n">
         <v>46.13</v>
@@ -1254,7 +1254,7 @@
         <v>46.14</v>
       </c>
       <c r="O9" t="n">
-        <v>2177103723500</v>
+        <v>2244581827250</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1263,7 +1263,7 @@
         <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>-839000</v>
+        <v>-847000</v>
       </c>
       <c r="S9" t="n">
         <v>77000</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17100</v>
+        <v>17110</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.44%</t>
+          <t>'-1.38%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.48</v>
       </c>
       <c r="E10" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H10" t="n">
         <v>3.77</v>
@@ -1346,7 +1346,7 @@
         <v>3.29</v>
       </c>
       <c r="O10" t="n">
-        <v>48404906135</v>
+        <v>48570116100</v>
       </c>
       <c r="P10" t="n">
         <v>22450</v>
@@ -1355,23 +1355,23 @@
         <v>6320</v>
       </c>
       <c r="R10" t="n">
-        <v>-11000</v>
+        <v>-30000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>보안주 상승 및 AI 관련 긍정적 뉴스 언급. 주가 조작 및 최악의 무빙에 대한 불만도 제기.</t>
+          <t>나스닥 폭락에도 불구하고 보안주 상승세 확인. AI 에이전트 해킹 및 무단 거래 우려 확산.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '주가 조작']</t>
+          <t>['보안주', 'AI', '해킹']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7110</v>
+        <v>7100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.66%</t>
+          <t>'-1.80%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F11" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="H11" t="n">
         <v>25.42</v>
@@ -1438,7 +1438,7 @@
         <v>25.47</v>
       </c>
       <c r="O11" t="n">
-        <v>11180938090</v>
+        <v>11568464820</v>
       </c>
       <c r="P11" t="n">
         <v>17950</v>
@@ -1447,14 +1447,14 @@
         <v>7010</v>
       </c>
       <c r="R11" t="n">
-        <v>26000</v>
+        <v>27000</v>
       </c>
       <c r="S11" t="n">
         <v>9000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3분기 순이익 7,556억 흑자 전환 및 재무 상태 개선을 근거로 주가 반등을 기대하는 게시글.</t>
+          <t>분기 순이익 7,556억으로 재무 상태 개선 확인. BPS 14천원대, PBR 0.8배 적용 시 11천원 거래 필요. 배당 200원 예정.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['순이익 흑자', '재무 개선', '주가 반등']</t>
+          <t>['순이익', 'BPS', '배당']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59000</v>
+        <v>16620</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.22%</t>
+          <t>'-4.04%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="F12" t="n">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="G12" t="n">
-        <v>649</v>
+        <v>221</v>
       </c>
       <c r="H12" t="n">
-        <v>22.25</v>
+        <v>27.89</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>61600</v>
+        <v>17320</v>
       </c>
       <c r="K12" t="n">
-        <v>59600</v>
+        <v>16810</v>
       </c>
       <c r="L12" t="n">
-        <v>60000</v>
+        <v>16850</v>
       </c>
       <c r="M12" t="n">
-        <v>57700</v>
+        <v>16450</v>
       </c>
       <c r="N12" t="n">
-        <v>22.26</v>
+        <v>27.87</v>
       </c>
       <c r="O12" t="n">
-        <v>97335885550</v>
+        <v>27072583510</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>16450</v>
       </c>
       <c r="R12" t="n">
-        <v>-203000</v>
+        <v>119000</v>
       </c>
       <c r="S12" t="n">
-        <v>-124000</v>
+        <v>30000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 이슈와 증시 폭락 가능성 언급 속 공매도 우려 및 주가 하락 전망.</t>
+          <t>조선주 전반의 하락세와 함께 민주당 정권 및 정치적 이슈에 대한 부정적인 언급이 다수 포함된 게시글.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '지수', '폭락']</t>
+          <t>['조선주 하락', '정치적 이슈', '주주 환원']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16580</v>
+        <v>58800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.27%</t>
+          <t>'-4.55%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>103</v>
+        <v>259</v>
       </c>
       <c r="F13" t="n">
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="G13" t="n">
-        <v>219</v>
+        <v>678</v>
       </c>
       <c r="H13" t="n">
-        <v>27.89</v>
+        <v>22.25</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17320</v>
+        <v>61600</v>
       </c>
       <c r="K13" t="n">
-        <v>16810</v>
+        <v>59600</v>
       </c>
       <c r="L13" t="n">
-        <v>16850</v>
+        <v>60000</v>
       </c>
       <c r="M13" t="n">
-        <v>16450</v>
+        <v>57700</v>
       </c>
       <c r="N13" t="n">
-        <v>27.87</v>
+        <v>22.26</v>
       </c>
       <c r="O13" t="n">
-        <v>26281442770</v>
+        <v>99788673250</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>16450</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>111000</v>
+        <v>-203000</v>
       </c>
       <c r="S13" t="n">
-        <v>30000</v>
+        <v>-124000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>조선주 전반의 하락세와 함께 민주당 정권 및 정치적 이슈에 대한 부정적인 언급이 다수 포함된 게시글.</t>
+          <t>정치적 이슈와 증시 폭락 가능성 언급 속 공매도 우려 및 주가 하락 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['조선주 하락', '정치적 이슈', '주주 환원']</t>
+          <t>['공매도', '지수', '폭락']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9310</v>
+        <v>9210</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-7.73%</t>
+          <t>'-8.72%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-1.19</v>
       </c>
       <c r="E14" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F14" t="n">
         <v>69</v>
       </c>
       <c r="G14" t="n">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="H14" t="n">
         <v>2.5</v>
@@ -1714,7 +1714,7 @@
         <v>3.69</v>
       </c>
       <c r="O14" t="n">
-        <v>45449588605</v>
+        <v>46053950585</v>
       </c>
       <c r="P14" t="n">
         <v>11690</v>
@@ -1723,7 +1723,7 @@
         <v>2270</v>
       </c>
       <c r="R14" t="n">
-        <v>-33000</v>
+        <v>13000</v>
       </c>
       <c r="S14" t="n">
         <v>1000</v>

--- a/data/trending_integrated_20261023_13.xlsx
+++ b/data/trending_integrated_20261023_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1933</v>
+        <v>1928</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+18.23%</t>
+          <t>'+17.92%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.14</v>
       </c>
       <c r="E2" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F2" t="n">
         <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="H2" t="n">
         <v>4.87</v>
@@ -610,7 +610,7 @@
         <v>5.01</v>
       </c>
       <c r="O2" t="n">
-        <v>63502250851</v>
+        <v>66004898243</v>
       </c>
       <c r="P2" t="n">
         <v>4980</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>휴머노이드 배터리 충전 상용화 및 빅웨이브 로봇 CES 참여 기대감. 외인 매수세 유입.</t>
+          <t>로봇 관련 기술 상용화 기대감과 대기업 협력 호재가 부각되며, 주가 상승에 대한 긍정적 전망과 매수 기회 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['휴머노이드', '빅웨이브', '외인매수']</t>
+          <t>['로봇', '상용화', '호재']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61100</v>
+        <v>61000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+10.29%</t>
+          <t>'+10.11%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="F3" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G3" t="n">
-        <v>1037</v>
+        <v>1068</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>609364133950</v>
+        <v>617116062500</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4055</v>
+        <v>3995</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.13%</t>
+          <t>'+6.53%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="F4" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="G4" t="n">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>146638727190</v>
+        <v>148329446452</v>
       </c>
       <c r="P4" t="n">
         <v>7050</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1248000</v>
+        <v>1258000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.04%</t>
+          <t>'+2.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>540</v>
       </c>
       <c r="G5" t="n">
-        <v>1327</v>
+        <v>1406</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>2951084235000</v>
+        <v>2990581587500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>국민연금 관련 논란 및 호남 반도체 중단 언급. 주가 반등 및 상승 추세 기대.</t>
+          <t>정치적 이슈와 지역 갈등 언급이 혼재하며, 단기적인 주가 변동성과 정치적 영향에 대한 우려가 공존.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['국민연금', '호남반도체', '주가반등']</t>
+          <t>['정치', '지역 갈등', '주가 변동성']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8710</v>
+        <v>13450</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.35%</t>
+          <t>'+0.82%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.04</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>199</v>
+        <v>450</v>
       </c>
       <c r="H6" t="n">
-        <v>5.11</v>
+        <v>2.92</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>8680</v>
+        <v>13340</v>
       </c>
       <c r="K6" t="n">
-        <v>9410</v>
+        <v>12840</v>
       </c>
       <c r="L6" t="n">
-        <v>9460</v>
+        <v>13700</v>
       </c>
       <c r="M6" t="n">
-        <v>8640</v>
+        <v>12530</v>
       </c>
       <c r="N6" t="n">
-        <v>5.15</v>
+        <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>6526148710</v>
+        <v>59263485890</v>
       </c>
       <c r="P6" t="n">
-        <v>15900</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>6310</v>
+        <v>1640</v>
       </c>
       <c r="R6" t="n">
-        <v>-334000</v>
+        <v>-190000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>뇌졸중 치료제 관련 특허 보유 및 3상 성공 가능성 언급. 신약 개발 외자 유치 및 합병 기대감.</t>
+          <t>유리기판 관련 기술력과 삼성전자 인수설이 부각되며, 광섬유 품귀 현상과 함께 주가 상승에 대한 기대감이 높음.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['뇌졸중치료제', '특허', '신약개발']</t>
+          <t>['유리기판', '인수설', '광섬유']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13330</v>
+        <v>8720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.07%</t>
+          <t>'+0.46%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>434</v>
+        <v>199</v>
       </c>
       <c r="H7" t="n">
-        <v>2.92</v>
+        <v>5.11</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13340</v>
+        <v>8680</v>
       </c>
       <c r="K7" t="n">
-        <v>12840</v>
+        <v>9410</v>
       </c>
       <c r="L7" t="n">
-        <v>13700</v>
+        <v>9460</v>
       </c>
       <c r="M7" t="n">
-        <v>12530</v>
+        <v>8640</v>
       </c>
       <c r="N7" t="n">
-        <v>3.48</v>
+        <v>5.15</v>
       </c>
       <c r="O7" t="n">
-        <v>58767527235</v>
+        <v>6541117410</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>15900</v>
       </c>
       <c r="Q7" t="n">
-        <v>1640</v>
+        <v>6310</v>
       </c>
       <c r="R7" t="n">
-        <v>-190000</v>
+        <v>-334000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>EUV 유리기판 관련 기술성 및 삼성 인수설 언급. 광섬유 품귀 현상과 외인 매수세 확인.</t>
+          <t>뇌졸중 치료제 관련 특허 보유 및 3상 성공 가능성 언급. 신약 개발 외자 유치 및 합병 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유리기판', '삼성인수', '광섬유']</t>
+          <t>['뇌졸중치료제', '특허', '신약개발']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14470</v>
+        <v>14510</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.41%</t>
+          <t>'-0.14%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F8" t="n">
         <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H8" t="n">
         <v>9.890000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>25977928745</v>
+        <v>26381608745</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3분기 실적 언급과 함께 주가 조작 및 이재명 대통령에 대한 강한 비판이 주를 이루는 게시글.</t>
+          <t>실적 발표 및 주가 조작 관련 의혹 제기가 있으며, 공매도와 대차거래 해지에 대한 주주들의 요청이 혼재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가 조작', '실적 발표', '대통령 비판']</t>
+          <t>['실적', '주가 조작', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>212500</v>
+        <v>213750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.93%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="G9" t="n">
-        <v>1600</v>
+        <v>1615</v>
       </c>
       <c r="H9" t="n">
         <v>46.13</v>
@@ -1254,7 +1254,7 @@
         <v>46.14</v>
       </c>
       <c r="O9" t="n">
-        <v>2244581827250</v>
+        <v>2281696974000</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>이재명 정부의 정책에 대한 부정적 언급과 함께 시장 붕괴 가능성, 일부 반도체 주 상승 기대감이 혼재된 게시글.</t>
+          <t>정치적 이슈와 일부 투자 심리가 혼재된 가운데, 일부 반등 기대감도 있으나 전반적인 시장 불안감 속에서 보수적인 관망세.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['시장 붕괴', '정책 비판', '반도체 주']</t>
+          <t>['정치', '시장 불안', '반등 기대']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17110</v>
+        <v>7120</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.38%</t>
+          <t>'-1.52%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.48</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="F10" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G10" t="n">
-        <v>147</v>
+        <v>463</v>
       </c>
       <c r="H10" t="n">
-        <v>3.77</v>
+        <v>25.42</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17350</v>
+        <v>7230</v>
       </c>
       <c r="K10" t="n">
-        <v>18130</v>
+        <v>7100</v>
       </c>
       <c r="L10" t="n">
-        <v>19070</v>
+        <v>7220</v>
       </c>
       <c r="M10" t="n">
-        <v>16530</v>
+        <v>7010</v>
       </c>
       <c r="N10" t="n">
-        <v>3.29</v>
+        <v>25.47</v>
       </c>
       <c r="O10" t="n">
-        <v>48570116100</v>
+        <v>11805862610</v>
       </c>
       <c r="P10" t="n">
-        <v>22450</v>
+        <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>6320</v>
+        <v>7010</v>
       </c>
       <c r="R10" t="n">
-        <v>-30000</v>
+        <v>27000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>나스닥 폭락에도 불구하고 보안주 상승세 확인. AI 에이전트 해킹 및 무단 거래 우려 확산.</t>
+          <t>분기 순이익 7,556억으로 재무 상태 개선 확인. BPS 14천원대, PBR 0.8배 적용 시 11천원 거래 필요. 배당 200원 예정.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '해킹']</t>
+          <t>['순이익', 'BPS', '배당']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7100</v>
+        <v>17000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.80%</t>
+          <t>'-2.02%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.05</v>
+        <v>0.48</v>
       </c>
       <c r="E11" t="n">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G11" t="n">
-        <v>452</v>
+        <v>147</v>
       </c>
       <c r="H11" t="n">
-        <v>25.42</v>
+        <v>3.77</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7230</v>
+        <v>17350</v>
       </c>
       <c r="K11" t="n">
-        <v>7100</v>
+        <v>18130</v>
       </c>
       <c r="L11" t="n">
-        <v>7220</v>
+        <v>19070</v>
       </c>
       <c r="M11" t="n">
-        <v>7010</v>
+        <v>16530</v>
       </c>
       <c r="N11" t="n">
-        <v>25.47</v>
+        <v>3.29</v>
       </c>
       <c r="O11" t="n">
-        <v>11568464820</v>
+        <v>48810628590</v>
       </c>
       <c r="P11" t="n">
-        <v>17950</v>
+        <v>22450</v>
       </c>
       <c r="Q11" t="n">
-        <v>7010</v>
+        <v>6320</v>
       </c>
       <c r="R11" t="n">
-        <v>27000</v>
+        <v>-30000</v>
       </c>
       <c r="S11" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>분기 순이익 7,556억으로 재무 상태 개선 확인. BPS 14천원대, PBR 0.8배 적용 시 11천원 거래 필요. 배당 200원 예정.</t>
+          <t>나스닥 폭락에도 불구하고 보안주 상승세 확인. AI 에이전트 해킹 및 무단 거래 우려 확산.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['순이익', 'BPS', '배당']</t>
+          <t>['보안주', 'AI', '해킹']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16620</v>
+        <v>16630</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.04%</t>
+          <t>'-3.98%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G12" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H12" t="n">
         <v>27.89</v>
@@ -1530,7 +1530,7 @@
         <v>27.87</v>
       </c>
       <c r="O12" t="n">
-        <v>27072583510</v>
+        <v>27822815450</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>58800</v>
+        <v>59000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.55%</t>
+          <t>'-4.22%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F13" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G13" t="n">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="H13" t="n">
         <v>22.25</v>
@@ -1622,7 +1622,7 @@
         <v>22.26</v>
       </c>
       <c r="O13" t="n">
-        <v>99788673250</v>
+        <v>101626366950</v>
       </c>
       <c r="P13" t="n">
         <v>139200</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈와 증시 폭락 가능성 언급 속 공매도 우려 및 주가 하락 전망.</t>
+          <t>정치적 비판과 함께 주가 하락에 대한 우려가 제기되며, 일부 반등 가능성 언급도 있으나 전반적으로 부정적 전망이 우세.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '지수', '폭락']</t>
+          <t>['정치', '주가 하락', '반등 가능성']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9210</v>
+        <v>9240</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-8.72%</t>
+          <t>'-8.42%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-1.19</v>
       </c>
       <c r="E14" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F14" t="n">
         <v>69</v>
       </c>
       <c r="G14" t="n">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="H14" t="n">
         <v>2.5</v>
@@ -1714,7 +1714,7 @@
         <v>3.69</v>
       </c>
       <c r="O14" t="n">
-        <v>46053950585</v>
+        <v>46364525765</v>
       </c>
       <c r="P14" t="n">
         <v>11690</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 하락 및 조정, 횡보 전망. 시장 및 종목 자체에 대한 부정적 분석.</t>
+          <t>주가 하락에 대한 부정적 전망이 지배적이며, 조정 및 횡보 가능성이 언급되고 일부에서는 매도 신호 포착.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['하락 전망', '조정', '횡보']</t>
+          <t>['주가 하락', '조정', '매도 신호']</t>
         </is>
       </c>
       <c r="X14" t="n">

--- a/data/trending_integrated_20261023_13.xlsx
+++ b/data/trending_integrated_20261023_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1928</v>
+        <v>1920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.92%</t>
+          <t>'+17.43%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.14</v>
       </c>
       <c r="E2" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="H2" t="n">
         <v>4.87</v>
@@ -610,7 +610,7 @@
         <v>5.01</v>
       </c>
       <c r="O2" t="n">
-        <v>66004898243</v>
+        <v>67363238982</v>
       </c>
       <c r="P2" t="n">
         <v>4980</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇 관련 기술 상용화 기대감과 대기업 협력 호재가 부각되며, 주가 상승에 대한 긍정적 전망과 매수 기회 언급.</t>
+          <t>휴머노이드, CES 관련 호재 언급과 함께 급등 기대감이 높으나, 일부는 하락 및 물량 확보를 위한 의도적 눌림으로 해석하고 있어 혼조세를 보임.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇', '상용화', '호재']</t>
+          <t>['휴머노이드', 'CES', '빅웨이브']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61000</v>
+        <v>60800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+10.11%</t>
+          <t>'+9.75%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="F3" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G3" t="n">
-        <v>1068</v>
+        <v>1088</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>617116062500</v>
+        <v>626952420600</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3995</v>
+        <v>3985</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.53%</t>
+          <t>'+6.27%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="F4" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G4" t="n">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>148329446452</v>
+        <v>149445451617</v>
       </c>
       <c r="P4" t="n">
         <v>7050</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1258000</v>
+        <v>1256000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.86%</t>
+          <t>'+2.70%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G5" t="n">
-        <v>1406</v>
+        <v>1457</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>2990581587500</v>
+        <v>3044176334000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 이슈와 지역 갈등 언급이 혼재하며, 단기적인 주가 변동성과 정치적 영향에 대한 우려가 공존.</t>
+          <t>정치적 이슈 및 지역 감정 관련 언급과 함께, 일부는 상승을, 일부는 하락을 예측하며 혼조세를 보임.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['정치', '지역 갈등', '주가 변동성']</t>
+          <t>['호남 반도체', '외인 투매', '하락 끝']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13450</v>
+        <v>8720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.82%</t>
+          <t>'+0.46%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="H6" t="n">
-        <v>2.92</v>
+        <v>5.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13340</v>
+        <v>8680</v>
       </c>
       <c r="K6" t="n">
-        <v>12840</v>
+        <v>9410</v>
       </c>
       <c r="L6" t="n">
-        <v>13700</v>
+        <v>9460</v>
       </c>
       <c r="M6" t="n">
-        <v>12530</v>
+        <v>8640</v>
       </c>
       <c r="N6" t="n">
-        <v>3.48</v>
+        <v>5.15</v>
       </c>
       <c r="O6" t="n">
-        <v>59263485890</v>
+        <v>6567340095</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>15900</v>
       </c>
       <c r="Q6" t="n">
-        <v>1640</v>
+        <v>6310</v>
       </c>
       <c r="R6" t="n">
-        <v>-190000</v>
+        <v>-334000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>유리기판 관련 기술력과 삼성전자 인수설이 부각되며, 광섬유 품귀 현상과 함께 주가 상승에 대한 기대감이 높음.</t>
+          <t>뇌졸중 치료제 관련 특허 보유 및 3상 성공 가능성 언급. 신약 개발 외자 유치 및 합병 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유리기판', '인수설', '광섬유']</t>
+          <t>['뇌졸중치료제', '특허', '신약개발']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8720</v>
+        <v>13400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.46%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.04</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
-        <v>199</v>
+        <v>451</v>
       </c>
       <c r="H7" t="n">
-        <v>5.11</v>
+        <v>2.92</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8680</v>
+        <v>13340</v>
       </c>
       <c r="K7" t="n">
-        <v>9410</v>
+        <v>12840</v>
       </c>
       <c r="L7" t="n">
-        <v>9460</v>
+        <v>13700</v>
       </c>
       <c r="M7" t="n">
-        <v>8640</v>
+        <v>12530</v>
       </c>
       <c r="N7" t="n">
-        <v>5.15</v>
+        <v>3.48</v>
       </c>
       <c r="O7" t="n">
-        <v>6541117410</v>
+        <v>59646006320</v>
       </c>
       <c r="P7" t="n">
-        <v>15900</v>
+        <v>31500</v>
       </c>
       <c r="Q7" t="n">
-        <v>6310</v>
+        <v>1640</v>
       </c>
       <c r="R7" t="n">
-        <v>-334000</v>
+        <v>-190000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>뇌졸중 치료제 관련 특허 보유 및 3상 성공 가능성 언급. 신약 개발 외자 유치 및 합병 기대감.</t>
+          <t>유리기판 관련 기술력과 삼성전자 인수설이 부각되며, 광섬유 품귀 현상과 함께 주가 상승에 대한 기대감이 높음.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['뇌졸중치료제', '특허', '신약개발']</t>
+          <t>['유리기판', '인수설', '광섬유']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14510</v>
+        <v>14540</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.14%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H8" t="n">
         <v>9.890000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>26381608745</v>
+        <v>26792682530</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>213750</v>
+        <v>213000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'-0.70%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="G9" t="n">
-        <v>1615</v>
+        <v>1639</v>
       </c>
       <c r="H9" t="n">
         <v>46.13</v>
@@ -1254,7 +1254,7 @@
         <v>46.14</v>
       </c>
       <c r="O9" t="n">
-        <v>2281696974000</v>
+        <v>2332852765250</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 이슈와 일부 투자 심리가 혼재된 가운데, 일부 반등 기대감도 있으나 전반적인 시장 불안감 속에서 보수적인 관망세.</t>
+          <t>정치적 이슈와 개인적인 투자 경험 언급 속 혼재된 투자 심리. 일부는 급등을 기대하나, 거시 경제 불안으로 인한 시장 붕괴 가능성도 제기됨.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['정치', '시장 불안', '반등 기대']</t>
+          <t>['시장 교란', '추세 전환', '매수 구간']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F10" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G10" t="n">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="H10" t="n">
         <v>25.42</v>
@@ -1346,7 +1346,7 @@
         <v>25.47</v>
       </c>
       <c r="O10" t="n">
-        <v>11805862610</v>
+        <v>12048937240</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>분기 순이익 7,556억으로 재무 상태 개선 확인. BPS 14천원대, PBR 0.8배 적용 시 11천원 거래 필요. 배당 200원 예정.</t>
+          <t>분기 순이익 흑자 전환 및 재무 상태 개선에도 불구하고, 목표가 하향 및 공매도 이슈로 인해 부정적인 전망이 우세함.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['순이익', 'BPS', '배당']</t>
+          <t>['분기 순이익', '목표가 하향', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17000</v>
+        <v>17010</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.02%</t>
+          <t>'-1.96%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>54</v>
       </c>
       <c r="G11" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H11" t="n">
         <v>3.77</v>
@@ -1438,7 +1438,7 @@
         <v>3.29</v>
       </c>
       <c r="O11" t="n">
-        <v>48810628590</v>
+        <v>48982916810</v>
       </c>
       <c r="P11" t="n">
         <v>22450</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16630</v>
+        <v>16740</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.98%</t>
+          <t>'-3.35%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F12" t="n">
         <v>69</v>
       </c>
       <c r="G12" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H12" t="n">
         <v>27.89</v>
@@ -1530,7 +1530,7 @@
         <v>27.87</v>
       </c>
       <c r="O12" t="n">
-        <v>27822815450</v>
+        <v>29333348900</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1590,13 +1590,13 @@
         <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F13" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G13" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H13" t="n">
         <v>22.25</v>
@@ -1622,7 +1622,7 @@
         <v>22.26</v>
       </c>
       <c r="O13" t="n">
-        <v>101626366950</v>
+        <v>104132270850</v>
       </c>
       <c r="P13" t="n">
         <v>139200</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9240</v>
+        <v>9250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-8.42%</t>
+          <t>'-8.33%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-1.19</v>
       </c>
       <c r="E14" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G14" t="n">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="H14" t="n">
         <v>2.5</v>
@@ -1714,7 +1714,7 @@
         <v>3.69</v>
       </c>
       <c r="O14" t="n">
-        <v>46364525765</v>
+        <v>46943113915</v>
       </c>
       <c r="P14" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261023_13.xlsx
+++ b/data/trending_integrated_20261023_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1920</v>
+        <v>1913</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.43%</t>
+          <t>'+17.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.14</v>
       </c>
       <c r="E2" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F2" t="n">
         <v>65</v>
       </c>
       <c r="G2" t="n">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="H2" t="n">
         <v>4.87</v>
@@ -610,7 +610,7 @@
         <v>5.01</v>
       </c>
       <c r="O2" t="n">
-        <v>67363238982</v>
+        <v>69545217447</v>
       </c>
       <c r="P2" t="n">
         <v>4980</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>진양산업</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60800</v>
+        <v>4575</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.75%</t>
+          <t>'+8.16%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.18</v>
+        <v>-0.76</v>
       </c>
       <c r="E3" t="n">
-        <v>360</v>
+        <v>81</v>
       </c>
       <c r="F3" t="n">
-        <v>193</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
-        <v>1088</v>
+        <v>116</v>
       </c>
       <c r="H3" t="n">
-        <v>38.9</v>
+        <v>2.67</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>55400</v>
+        <v>4230</v>
       </c>
       <c r="K3" t="n">
-        <v>56300</v>
+        <v>4355</v>
       </c>
       <c r="L3" t="n">
-        <v>61300</v>
+        <v>4820</v>
       </c>
       <c r="M3" t="n">
-        <v>56200</v>
+        <v>4210</v>
       </c>
       <c r="N3" t="n">
-        <v>37.72</v>
+        <v>3.43</v>
       </c>
       <c r="O3" t="n">
-        <v>626952420600</v>
+        <v>9325671904</v>
       </c>
       <c r="P3" t="n">
-        <v>67300</v>
+        <v>8020</v>
       </c>
       <c r="Q3" t="n">
-        <v>23150</v>
+        <v>3660</v>
       </c>
       <c r="R3" t="n">
-        <v>1522000</v>
+        <v>-112000</v>
       </c>
       <c r="S3" t="n">
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인/기관의 대규모 매수 유입 및 자사주 매입/소각 공시 기반 상승 전망.</t>
+          <t>무죄 판결 가능성에 대한 기대와 함께 물량 털어내기에 대한 언급이 있음. 법 전문가들의 의견과 대법원 관련 예상, 그리고 증거재판주의에 대한 논의가 이루어짐.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['자사주', '매입', '공시']</t>
+          <t>['무죄', '대법원', '증거재판주의']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>003780</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3985</v>
+        <v>59900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.27%</t>
+          <t>'+8.12%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="E4" t="n">
-        <v>309</v>
+        <v>372</v>
       </c>
       <c r="F4" t="n">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="G4" t="n">
-        <v>845</v>
+        <v>1097</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>38.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3750</v>
+        <v>55400</v>
       </c>
       <c r="K4" t="n">
-        <v>3905</v>
+        <v>56300</v>
       </c>
       <c r="L4" t="n">
-        <v>4550</v>
+        <v>61300</v>
       </c>
       <c r="M4" t="n">
-        <v>3815</v>
+        <v>56200</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>37.72</v>
       </c>
       <c r="O4" t="n">
-        <v>149445451617</v>
+        <v>641761397150</v>
       </c>
       <c r="P4" t="n">
-        <v>7050</v>
+        <v>67300</v>
       </c>
       <c r="Q4" t="n">
-        <v>2500</v>
+        <v>23150</v>
       </c>
       <c r="R4" t="n">
-        <v>-251000</v>
+        <v>1522000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 리스크 부각과 함께 방산주로서의 상승 가능성을 언급하는 게시글.</t>
+          <t>외인/기관의 대규모 매수 유입 및 자사주 매입/소각 공시 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['북한 리스크', '방산주', '김정은']</t>
+          <t>['자사주', '매입', '공시']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1256000</v>
+        <v>3980</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.70%</t>
+          <t>'+6.13%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>314</v>
       </c>
       <c r="F5" t="n">
-        <v>537</v>
+        <v>166</v>
       </c>
       <c r="G5" t="n">
-        <v>1457</v>
+        <v>850</v>
       </c>
       <c r="H5" t="n">
-        <v>48.77</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1223000</v>
+        <v>3750</v>
       </c>
       <c r="K5" t="n">
-        <v>1200000</v>
+        <v>3905</v>
       </c>
       <c r="L5" t="n">
-        <v>1263000</v>
+        <v>4550</v>
       </c>
       <c r="M5" t="n">
-        <v>1171000</v>
+        <v>3815</v>
       </c>
       <c r="N5" t="n">
-        <v>48.79</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3044176334000</v>
+        <v>150148754774</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>7050</v>
       </c>
       <c r="Q5" t="n">
-        <v>468000</v>
+        <v>2500</v>
       </c>
       <c r="R5" t="n">
-        <v>-405000</v>
+        <v>-251000</v>
       </c>
       <c r="S5" t="n">
-        <v>166000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 지역 감정 관련 언급과 함께, 일부는 상승을, 일부는 하락을 예측하며 혼조세를 보임.</t>
+          <t>북한 관련 지정학적 리스크 부각과 함께 방산주로서의 상승 가능성을 언급하는 게시글.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['호남 반도체', '외인 투매', '하락 끝']</t>
+          <t>['북한 리스크', '방산주', '김정은']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8720</v>
+        <v>1250000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.46%</t>
+          <t>'+2.21%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>107</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>529</v>
       </c>
       <c r="G6" t="n">
-        <v>200</v>
+        <v>1535</v>
       </c>
       <c r="H6" t="n">
-        <v>5.11</v>
+        <v>48.77</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>8680</v>
+        <v>1223000</v>
       </c>
       <c r="K6" t="n">
-        <v>9410</v>
+        <v>1200000</v>
       </c>
       <c r="L6" t="n">
-        <v>9460</v>
+        <v>1263000</v>
       </c>
       <c r="M6" t="n">
-        <v>8640</v>
+        <v>1171000</v>
       </c>
       <c r="N6" t="n">
-        <v>5.15</v>
+        <v>48.79</v>
       </c>
       <c r="O6" t="n">
-        <v>6567340095</v>
+        <v>3103137811000</v>
       </c>
       <c r="P6" t="n">
-        <v>15900</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>6310</v>
+        <v>468000</v>
       </c>
       <c r="R6" t="n">
-        <v>-334000</v>
+        <v>-405000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>166000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>뇌졸중 치료제 관련 특허 보유 및 3상 성공 가능성 언급. 신약 개발 외자 유치 및 합병 기대감.</t>
+          <t>국민연금의 자금 운용 및 호남 반도체 중단 선언 이슈에 대한 언급이 있으며, 솔리다임 상장 철회 시 300 가는 호재로 기대. 외인 주도 상승과 밤샘 넥장 우상향 전망이 제시됨.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['뇌졸중치료제', '특허', '신약개발']</t>
+          <t>['국민연금', '솔리다임', '반도체']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13400</v>
+        <v>13430</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.45%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>98</v>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="H7" t="n">
         <v>2.92</v>
@@ -1070,7 +1070,7 @@
         <v>3.48</v>
       </c>
       <c r="O7" t="n">
-        <v>59646006320</v>
+        <v>60361305975</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유리기판 관련 기술력과 삼성전자 인수설이 부각되며, 광섬유 품귀 현상과 함께 주가 상승에 대한 기대감이 높음.</t>
+          <t>유리기판 관련 기술력과 삼성전자 인수합병 가능성에 대한 기대감이 높음. 광섬유 품귀 현상과 외인 매수세 유입에 따른 긍정적 전망이 제시되며, 미국 통신주 하락에도 불구하고 상승 가능성을 주장함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유리기판', '인수설', '광섬유']</t>
+          <t>['유리기판', '인수합병', '광섬유']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14540</v>
+        <v>8710</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'+0.35%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="H8" t="n">
-        <v>9.890000000000001</v>
+        <v>5.11</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14530</v>
+        <v>8680</v>
       </c>
       <c r="K8" t="n">
-        <v>14190</v>
+        <v>9410</v>
       </c>
       <c r="L8" t="n">
-        <v>14710</v>
+        <v>9460</v>
       </c>
       <c r="M8" t="n">
-        <v>13810</v>
+        <v>8640</v>
       </c>
       <c r="N8" t="n">
-        <v>9.949999999999999</v>
+        <v>5.15</v>
       </c>
       <c r="O8" t="n">
-        <v>26792682530</v>
+        <v>6588293485</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>15900</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>6310</v>
       </c>
       <c r="R8" t="n">
-        <v>-62000</v>
+        <v>-334000</v>
       </c>
       <c r="S8" t="n">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>실적 발표 및 주가 조작 관련 의혹 제기가 있으며, 공매도와 대차거래 해지에 대한 주주들의 요청이 혼재.</t>
+          <t>뇌졸중 치료제 관련 특허 보유 및 3상 성공 가능성 언급. 신약 개발 외자 유치 및 합병 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['실적', '주가 조작', '공매도']</t>
+          <t>['뇌졸중치료제', '특허', '신약개발']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>213000</v>
+        <v>14520</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.70%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>114</v>
       </c>
       <c r="F9" t="n">
-        <v>486</v>
+        <v>39</v>
       </c>
       <c r="G9" t="n">
-        <v>1639</v>
+        <v>195</v>
       </c>
       <c r="H9" t="n">
-        <v>46.13</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>214500</v>
+        <v>14530</v>
       </c>
       <c r="K9" t="n">
-        <v>206000</v>
+        <v>14190</v>
       </c>
       <c r="L9" t="n">
-        <v>214500</v>
+        <v>14710</v>
       </c>
       <c r="M9" t="n">
-        <v>203500</v>
+        <v>13810</v>
       </c>
       <c r="N9" t="n">
-        <v>46.14</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>2332852765250</v>
+        <v>27252937640</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>-847000</v>
+        <v>-62000</v>
       </c>
       <c r="S9" t="n">
-        <v>77000</v>
+        <v>69000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 이슈와 개인적인 투자 경험 언급 속 혼재된 투자 심리. 일부는 급등을 기대하나, 거시 경제 불안으로 인한 시장 붕괴 가능성도 제기됨.</t>
+          <t>실적 발표 및 주가 조작 관련 의혹 제기가 있으며, 공매도와 대차거래 해지에 대한 주주들의 요청이 혼재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['시장 교란', '추세 전환', '매수 구간']</t>
+          <t>['실적', '주가 조작', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7120</v>
+        <v>212750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.52%</t>
+          <t>'-0.82%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>148</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>65</v>
+        <v>491</v>
       </c>
       <c r="G10" t="n">
-        <v>474</v>
+        <v>1670</v>
       </c>
       <c r="H10" t="n">
-        <v>25.42</v>
+        <v>46.13</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7230</v>
+        <v>214500</v>
       </c>
       <c r="K10" t="n">
-        <v>7100</v>
+        <v>206000</v>
       </c>
       <c r="L10" t="n">
-        <v>7220</v>
+        <v>214500</v>
       </c>
       <c r="M10" t="n">
-        <v>7010</v>
+        <v>203500</v>
       </c>
       <c r="N10" t="n">
-        <v>25.47</v>
+        <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>12048937240</v>
+        <v>2386052681250</v>
       </c>
       <c r="P10" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>7010</v>
+        <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>27000</v>
+        <v>-847000</v>
       </c>
       <c r="S10" t="n">
-        <v>9000</v>
+        <v>77000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>분기 순이익 흑자 전환 및 재무 상태 개선에도 불구하고, 목표가 하향 및 공매도 이슈로 인해 부정적인 전망이 우세함.</t>
+          <t>정치적 발언과 개인적인 평단가 언급이 주를 이루며, 일부 투자자들은 급등을 기대하는 반면 시장 붕괴 가능성을 경고함. ETF 시장 교란 및 연기금 매도에 대한 우려가 제기됨.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['분기 순이익', '목표가 하향', '공매도']</t>
+          <t>['ETF', '연기금', '반도체']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17010</v>
+        <v>17170</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.96%</t>
+          <t>'-1.04%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.48</v>
       </c>
       <c r="E11" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F11" t="n">
         <v>54</v>
       </c>
       <c r="G11" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H11" t="n">
         <v>3.77</v>
@@ -1438,7 +1438,7 @@
         <v>3.29</v>
       </c>
       <c r="O11" t="n">
-        <v>48982916810</v>
+        <v>49324652730</v>
       </c>
       <c r="P11" t="n">
         <v>22450</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>나스닥 폭락에도 불구하고 보안주 상승세 확인. AI 에이전트 해킹 및 무단 거래 우려 확산.</t>
+          <t>미국 보안주 폭등과 달리 국내 주가 흐름에 대한 불만이 제기되며, 위꼬리 음봉 패턴을 통한 물량 털어내기 의혹이 제기됨. AI 해킹 이슈와 보안주 상승 기대감이 있으나, 수급 부족 및 주가 조작 가능성에 대한 우려도 나타남.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '해킹']</t>
+          <t>['보안주', 'AI', '수급']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16740</v>
+        <v>7110</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.35%</t>
+          <t>'-1.66%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="F12" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G12" t="n">
-        <v>223</v>
+        <v>488</v>
       </c>
       <c r="H12" t="n">
-        <v>27.89</v>
+        <v>25.42</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17320</v>
+        <v>7230</v>
       </c>
       <c r="K12" t="n">
-        <v>16810</v>
+        <v>7100</v>
       </c>
       <c r="L12" t="n">
-        <v>16850</v>
+        <v>7220</v>
       </c>
       <c r="M12" t="n">
-        <v>16450</v>
+        <v>7010</v>
       </c>
       <c r="N12" t="n">
-        <v>27.87</v>
+        <v>25.47</v>
       </c>
       <c r="O12" t="n">
-        <v>29333348900</v>
+        <v>12356905285</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>17950</v>
       </c>
       <c r="Q12" t="n">
-        <v>16450</v>
+        <v>7010</v>
       </c>
       <c r="R12" t="n">
-        <v>119000</v>
+        <v>27000</v>
       </c>
       <c r="S12" t="n">
-        <v>30000</v>
+        <v>9000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>조선주 전반의 하락세와 함께 민주당 정권 및 정치적 이슈에 대한 부정적인 언급이 다수 포함된 게시글.</t>
+          <t>기대 이상의 분기 순이익 발표와 재무 상태 개선에 대한 긍정적 분석이 있으나, 공매도 및 목표가 하향 조정에 대한 우려도 공존. 내년 주가 상승 및 배당 기대, 무위험 수익 구간 분석 등이 제시됨.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['조선주 하락', '정치적 이슈', '주주 환원']</t>
+          <t>['순이익', '공매도', '배당']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59000</v>
+        <v>16740</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.22%</t>
+          <t>'-3.35%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>261</v>
+        <v>108</v>
       </c>
       <c r="F13" t="n">
-        <v>163</v>
+        <v>70</v>
       </c>
       <c r="G13" t="n">
-        <v>683</v>
+        <v>227</v>
       </c>
       <c r="H13" t="n">
-        <v>22.25</v>
+        <v>27.89</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>61600</v>
+        <v>17320</v>
       </c>
       <c r="K13" t="n">
-        <v>59600</v>
+        <v>16810</v>
       </c>
       <c r="L13" t="n">
-        <v>60000</v>
+        <v>16850</v>
       </c>
       <c r="M13" t="n">
-        <v>57700</v>
+        <v>16450</v>
       </c>
       <c r="N13" t="n">
-        <v>22.26</v>
+        <v>27.87</v>
       </c>
       <c r="O13" t="n">
-        <v>104132270850</v>
+        <v>30338446535</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>16450</v>
       </c>
       <c r="R13" t="n">
-        <v>-203000</v>
+        <v>119000</v>
       </c>
       <c r="S13" t="n">
-        <v>-124000</v>
+        <v>30000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 비판과 함께 주가 하락에 대한 우려가 제기되며, 일부 반등 가능성 언급도 있으나 전반적으로 부정적 전망이 우세.</t>
+          <t>민주당 정권 시작 이후 주가 하락에 대한 불만이 제기되며, 조선주 전반의 약세와 신저점 경신에 대한 우려가 나타남. 주주환원 정책 발표 가능성에 대한 희망적 기대도 있음.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치', '주가 하락', '반등 가능성']</t>
+          <t>['조선주', '주주환원', '신저점']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,97 +1660,189 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9250</v>
+        <v>59100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-8.33%</t>
+          <t>'-4.06%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1.19</v>
+        <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>153</v>
+        <v>262</v>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>164</v>
       </c>
       <c r="G14" t="n">
-        <v>376</v>
+        <v>691</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5</v>
+        <v>22.25</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>10090</v>
+        <v>61600</v>
       </c>
       <c r="K14" t="n">
-        <v>9770</v>
+        <v>59600</v>
       </c>
       <c r="L14" t="n">
-        <v>10060</v>
+        <v>60000</v>
       </c>
       <c r="M14" t="n">
-        <v>8940</v>
+        <v>57700</v>
       </c>
       <c r="N14" t="n">
-        <v>3.69</v>
+        <v>22.26</v>
       </c>
       <c r="O14" t="n">
-        <v>46943113915</v>
+        <v>107076435400</v>
       </c>
       <c r="P14" t="n">
-        <v>11690</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>2270</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>13000</v>
+        <v>-203000</v>
       </c>
       <c r="S14" t="n">
-        <v>1000</v>
+        <v>-124000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 부정적 전망이 지배적이며, 조정 및 횡보 가능성이 언급되고 일부에서는 매도 신호 포착.</t>
+          <t>정치적 비판과 함께 주가 하락에 대한 우려가 제기되며, 일부 반등 가능성 언급도 있으나 전반적으로 부정적 전망이 우세.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['정치', '주가 하락', '반등 가능성']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>9220</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-8.62%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="E15" t="n">
+        <v>154</v>
+      </c>
+      <c r="F15" t="n">
+        <v>72</v>
+      </c>
+      <c r="G15" t="n">
+        <v>380</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>10090</v>
+      </c>
+      <c r="K15" t="n">
+        <v>9770</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10060</v>
+      </c>
+      <c r="M15" t="n">
+        <v>8940</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="O15" t="n">
+        <v>47286147535</v>
+      </c>
+      <c r="P15" t="n">
+        <v>11690</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R15" t="n">
+        <v>13000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>주가 하락에 대한 부정적 전망이 지배적이며, 조정 및 횡보 가능성이 언급되고 일부에서는 매도 신호 포착.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
         <v>0.1</v>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>['주가 하락', '조정', '매도 신호']</t>
         </is>
       </c>
-      <c r="X14" t="n">
+      <c r="X15" t="n">
         <v>6</v>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>396300</t>
         </is>
